--- a/光伏配储项目/电价数据/2026/上柏站.xlsx
+++ b/光伏配储项目/电价数据/2026/上柏站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.51158</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38456</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.7633</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.57485</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.6045499999999999</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.5210399999999999</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.51934</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43762</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45447</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.44459</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42373</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.42264</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40902</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39859</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.40125</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38488</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.4025</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42315</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41256</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.3546</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39147</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38498</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41694</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39218</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42077</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.4139</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.4239</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41333</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.4445</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.3679</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30007</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.34101</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.2737</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29505</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.30848</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.32397</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32825</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.13109</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.10648</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.1222</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.11195</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.05024</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.11234</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.16481</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.15873</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.11671</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.0916</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.04651</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.10376</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.04088</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.15352</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21723</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.25833</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.25601</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.24622</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.12103</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.008109999999999999</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.28746</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.14465</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.30795</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.28655</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.35662</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.31076</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.21649</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.34405</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.6632</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.55974</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.58545</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.38317</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.41284</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.62949</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.46736</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.44755</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.44339</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.58141</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.48177</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.64488</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.8295800000000001</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.64319</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.65859</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.8114</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.21784</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.43296</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.6941799999999999</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.6030599999999999</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.85294</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.65954</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.67026</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.65716</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.6277999999999999</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.4804</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.48071</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.39806</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41618</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42586</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32916</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.7127</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.77149</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.7971699999999999</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.53265</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.8552999999999999</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.53528</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.51838</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.5051</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.51064</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.48808</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40295</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.46961</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.38118</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.37996</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39069</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33683</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37012</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35553</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.36018</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37467</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37479</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35877</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.37977</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.4186</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.49886</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.60062</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.74354</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.4289</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.38366</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.43989</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34768</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.33626</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.43734</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.5258700000000001</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.17775</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.29814</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.37559</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.06874</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.36366</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.35886</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.34722</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.3757799999999999</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.3495</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.41253</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.50887</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.77095</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.23342</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.33473</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.37707</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.38974</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.39519</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.43497</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.81204</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.5422100000000001</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.35146</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.14245</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.28385</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.3223</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.3931</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.31581</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.31598</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.5251</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.34988</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.27513</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.36621</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.36132</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.26702</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.2823</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.45478</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.43654</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.29208</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.44532</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.37285</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.6549400000000001</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.7990700000000001</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.6425700000000001</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.69994</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.79015</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.74499</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.68208</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.6097</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.77652</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.5940599999999999</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.46033</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.06739</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.40072</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.47474</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.66862</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44434</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.4378</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.42349</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.35208</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.38105</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35843</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33461</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32145</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.51732</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.38329</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.53627</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.42843</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.38285</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.40496</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.41944</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38992</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38918</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36767</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43786</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.45456</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33842</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37065</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39621</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.37188</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37277</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35591</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36141</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35176</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36682</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35908</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38482</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39641</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47377</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.45443</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44868</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.35071</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.40121</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35296</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.37149</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.35037</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.48643</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.38936</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.39271</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.32785</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.22407</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.50759</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.26995</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.3192</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.31795</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.32188</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.3066</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.34442</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.47987</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.41096</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.519</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.3403</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.49182</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.43287</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.29544</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.17079</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.33164</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.28768</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.33621</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.31077</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.28546</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.29342</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.34034</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.29909</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.2791</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.40115</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.40633</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.42769</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.43559</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.52467</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.43069</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.51638</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.65062</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.39757</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.40576</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.35168</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.37064</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.57472</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.64855</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.7496900000000001</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.57585</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.33599</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.50712</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.45012</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.43116</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.49345</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.45595</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.47745</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.46325</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.42339</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.39376</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.44688</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.42374</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.4084100000000001</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.41348</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.37064</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34917</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34237</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31921</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.40588</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.43362</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.34719</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.36636</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.36265</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.35325</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.33495</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.32837</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.34674</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.31865</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.32253</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.46074</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.32809</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.32213</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.33042</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.32807</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.30343</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.30836</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.3046</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.2974</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.30504</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33922</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35402</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.35486</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.3893</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.33636</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.34184</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.31609</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.34224</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.35061</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.35619</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.29403</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.2812</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.32344</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.20865</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.22502</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.18426</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.3452</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.2682</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.29274</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.31125</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.52338</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.36578</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.45376</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.37719</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.10741</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.10529</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.17759</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.31657</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.28774</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.18951</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.23474</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.53515</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.07275</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.13133</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.24022</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.25292</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.37635</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.34065</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.28959</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.21906</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.23815</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.20294</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.26685</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.12281</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.2607</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.27067</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.29901</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.33658</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.30993</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.33831</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.35631</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.33141</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.39548</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.44141</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.663</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.47106</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.43182</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.36426</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.34478</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.35335</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.35725</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.3361</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.33098</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.30523</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31662</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32538</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.29653</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31412</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31814</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.30356</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.29986</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.30356</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.4134</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38203</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35645</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.30068</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.31139</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.3112</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.30743</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.30547</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.28985</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.30556</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.30624</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.28977</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.29401</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.28974</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.28974</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.28966</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.29795</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.29179</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.29479</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31231</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.30572</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31648</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.3244</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33278</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32619</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.27851</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.25926</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.05124</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.04009</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.05191</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.05354</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.04457</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.04189</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.04763000000000001</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.04335</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.03595</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.04703</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.04547</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.04817</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.04646</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.04547</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.04583</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.04759</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.04426</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.04661</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.04341</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.04192</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.04445</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.04558</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.21824</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.04059</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.04644</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05522</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.04974</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.0475</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.0038</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.01907</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.15881</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.05842</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.11532</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.29029</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.2937</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31999</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32958</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33547</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33578</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33591</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33518</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.38745</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.39223</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38764</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.3767</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34127</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.39939</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39987</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.4095</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46735</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.3546</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39624</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.39977</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41646</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35493</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35805</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34465</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35537</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35063</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36797</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.68041</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.39963</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.44501</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.42226</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.42215</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35972</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35858</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35812</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33213</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.30901</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.32289</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.35722</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.3515</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.3473</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.3459</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33486</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31421</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.32954</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33456</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32157</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.29996</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32147</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33514</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33827</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.34956</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35183</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34161</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31573</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10256</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04379</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04695000000000001</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04531</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04617</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04616</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04617</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04558</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.04611</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.09909</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>-0.004059999999999999</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.04482</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04384</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04555</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04356</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04326</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04548</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.0434</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04485</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04533</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.0436</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04416</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.04823</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.04995</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04455</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.0499</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04946</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.04729</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04769</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.20003</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14292</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.29022</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.3048</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.30011</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29521</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.2932</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29374</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29268</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29707</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29098</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29517</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26899</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29404</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29828</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.3087</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30402</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30226</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31455</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.3186</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34776</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34964</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34446</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36637</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.3649</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33545</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33027</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31765</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31056</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40436</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.34988</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32079</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30722</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.3147799999999999</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30148</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28129</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29438</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29088</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28814</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28101</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.2713</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27108</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28119</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17249</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.15873</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17102</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14778</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15951</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15867</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23627</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21409</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22664</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26885</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28585</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.2909</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31948</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29089</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28101</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28118</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28061</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27204</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28109</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32255</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.3103399999999999</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.31645</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30963</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35924</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31648</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29747</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.38359</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38008</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42849</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45601</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33199</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41856</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41546</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38909</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.4025899999999999</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30016</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30104</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29949</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.30008</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.1563</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29556</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31108</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.3135</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31398</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32191</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34654</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30082</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33097</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38558</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.50775</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.7909299999999999</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.62209</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.4001</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49806</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810900000000001</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92055</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49468</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.91565</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86634</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.2986</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35764</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.8915</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63244</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.19106</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.87076</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.54127</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33485</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.0357</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53472</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79425</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.52954</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77628</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7801399999999999</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87718</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87558</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49621</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.40169</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.40388</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.45347</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.21099</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87902</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55113</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62582</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.5393300000000001</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49887</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45635</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42477</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43789</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45017</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38921</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45279</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42007</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35224</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39999</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36519</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38607</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41462</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43357</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34376</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39023</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35055</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.3419700000000001</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.33553</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.34706</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.40326</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34962</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45079</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.354</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.4002</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.3996</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.58566</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42709</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.5956900000000001</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.60177</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.6626299999999999</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.47502</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.41939</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.5824199999999999</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.45232</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.8803200000000001</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.63101</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.87963</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.86217</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.86595</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.34932</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.44391</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.32786</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.33634</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30719</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.34609</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.46819</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.29526</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.29874</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31284</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35714</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33289</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32131</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.33655</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33735</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31807</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.30637</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31922</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31992</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.34367</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31519</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31499</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30365</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29593</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31221</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31368</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31221</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.31442</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.30996</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.31498</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.3222</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.32318</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.32454</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35432</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.34054</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.34017</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33788</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33041</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33723</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33519</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.40946</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41206</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45158</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.4144</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39108</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37455</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35328</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32839</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.9186599999999999</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36017</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.46463</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.3546</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.4088</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.46486</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.38048</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.40931</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.36083</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.3656</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.3491</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.34739</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38912</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33044</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35888</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34543</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32277</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.39951</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.49898</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.3568</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38714</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34323</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35054</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35492</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37025</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35766</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36276</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31633</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31356</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.3325</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33802</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33755</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.34927</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31479</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31577</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29078</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.30715</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.29104</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.30255</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.16643</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.31286</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30869</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.33076</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.32526</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.29707</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26271</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19901</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.27713</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.19362</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.31148</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.27855</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31137</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.3122799999999999</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.35887</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.35319</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.31258</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.31159</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.31991</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.30449</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.31137</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.29468</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.28928</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30747</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.32005</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.3154</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29007</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.34825</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.2557</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32178</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.27814</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.33926</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27645</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.35033</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32895</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.3409</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.30986</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.3189</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38538</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.33473</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.43206</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.34983</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.28179</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42315</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35078</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44768</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.32018</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.41989</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35877</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40112</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.39982</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.5949500000000001</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.34925</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.8899600000000001</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.33106</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.13848</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.6982699999999999</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.7885599999999999</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.6445</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.57765</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.44884</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.44991</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.49996</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.43948</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.4367</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41464</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41255</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42283</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.49919</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41256</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43368</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41211</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43371</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39011</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42704</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.44926</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39597</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.42313</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43311</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41256</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41259</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.39949</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42254</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.3955</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.40161</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.49414</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.36241</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.34602</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.29698</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.37131</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.37658</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.31461</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.35022</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.31208</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.37049</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.30319</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>1.13868</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.6307999999999999</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.40238</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.36893</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.25047</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>1.15314</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.6994</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.43093</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.3313</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.31898</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.78476</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.41938</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30893</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26263</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.26102</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.3142799999999999</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.29073</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.29132</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.30571</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.29702</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.31657</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.3209</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.34997</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31594</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.34016</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.34108</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.40979</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.39998</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.35216</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.36051</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.3402</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.33577</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.37529</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.3546</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.36317</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.36768</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36251</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.34926</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.57778</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.46188</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.7497699999999999</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.46389</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.43651</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.37466</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.41975</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38526</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36832</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33333</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.33978</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.3285</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32345</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31841</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.42131</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.33822</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34291</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.33787</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33479</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32442</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32768</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32441</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.3232</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.3222</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.30876</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32618</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32477</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31883</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.3149</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.31838</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.3093</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32418</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31031</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.31641</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.31895</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.39006</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32283</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.3487</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.39836</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37351</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.34895</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33799</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35382</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33131</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33391</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.3186</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.28316</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.3353</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.36443</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.33331</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.34798</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>1.37121</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.33182</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.27006</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.17069</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.17617</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.33643</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>1.18306</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.15243</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>1.16513</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>1.15262</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>1.16347</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>1.28855</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>1.16824</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>1.29732</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>1.16249</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.23241</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>1.13541</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>1.13768</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>1.21319</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.16141</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.16659</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.3218</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.34267</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.3447</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.38169</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.32015</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.39677</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.38286</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.45569</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34525</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37898</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34635</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.43079</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.3839</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.4483</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.3988</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.4202</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40054</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39635</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.44045</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.43831</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.43766</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44256</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44345</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40181</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.38983</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39702</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39086</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35873</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.35931</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34695</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34841</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.33882</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.53672</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38833</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.4670899999999999</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42253</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41465</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.3696</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.37992</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.37892</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39197</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.37927</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36971</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.37985</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.35976</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39062</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.36985</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.37979</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.34984</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.3469</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35482</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34448</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.33987</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34486</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.33987</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34451</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35442</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.36981</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.37979</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.35971</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.3399</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34005</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34007</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.3279</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34189</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.34872</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.36166</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29716</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31407</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31361</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30832</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29423</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.28208</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.27094</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.26555</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.20286</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.24961</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.24265</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.26936</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30047</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.28774</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31727</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.30275</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.28704</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.26739</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31219</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29369</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.27687</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.24136</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.3107</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.30656</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.29463</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.30529</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.2849100000000001</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.31599</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.33932</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.34012</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.3328</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.33838</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.33907</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.34728</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.36605</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.35624</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.3745</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.39115</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.3366</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.30507</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.34095</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.24252</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.3155</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.38124</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35655</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.35754</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35503</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.46448</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.32995</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.3509</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36695</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.369</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.35987</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.37965</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38003</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38475</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.34956</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.35982</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.33993</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36529</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.41593</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37034</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.39064</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.37947</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35212</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34875</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.35943</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35114</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34134</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34724</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34528</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.34902</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34598</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.33992</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.3415</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34265</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.3381</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33783</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33905</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33017</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.33988</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33148</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.34945</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.34351</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36165</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.31074</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.33122</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33874</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.32505</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.32134</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33537</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.32364</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.35577</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.41614</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.3926</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.3148</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.44537</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.51131</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.33758</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.44178</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.3102200000000001</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.30637</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.82886</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.59656</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.29798</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.24961</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.77627</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.12604</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.34467</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.30848</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.32329</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.3639</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.37361</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.35181</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.32671</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.32487</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.30643</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.32764</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.36483</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.38274</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.35415</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.43618</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.35763</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.35412</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.36119</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.36606</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.32873</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.42524</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.32996</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.33917</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.34879</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.35807</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.35279</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.44952</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.42612</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.7084600000000001</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.37569</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.38909</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.33094</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.31941</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.32185</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.5327499999999999</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.25872</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.38047</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.3093</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.31568</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.32827</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.32634</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.30136</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.30614</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.2846</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32182</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30503</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.3705</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.33385</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.327</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32454</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.32944</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.32435</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.32409</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.31813</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.32349</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.3246</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32354</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32672</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32778</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32648</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.3269</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32387</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33003</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32493</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32017</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31966</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32285</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32599</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.32972</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33434</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.3446</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.33968</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.33953</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33375</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33768</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32012</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.32028</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.3342</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34058</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.34514</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33452</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.32071</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.32251</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32482</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31709</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.34066</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.30011</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.34349</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34406</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.31237</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32451</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28027</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32518</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.31782</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32092</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32543</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32791</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33421</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33138</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.30121</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.32709</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.31947</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.3197</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.3202</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31514</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.35043</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.31574</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.32686</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.33155</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.37155</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.3474100000000001</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.3460299999999999</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33519</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.34983</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.34978</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.34976</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.35964</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.33393</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.32999</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.34467</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.36975</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36239</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.35455</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36047</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.3557</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.366</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.3593</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.38202</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38494</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37143</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.39785</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.3548</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.37851</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.36298</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.34911</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.34986</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34811</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34941</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33897</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.34989</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.34955</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35089</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35073</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35066</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.34986</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.3486</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34878</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34567</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.35696</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.3464100000000001</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.34692</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34861</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33666</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33904</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.33986</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.33893</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36805</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.3242</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33764</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33904</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.3486</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33603</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33887</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34486</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33526</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34863</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34863</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33583</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.33974</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32771</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.3477</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.34012</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33606</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.30557</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32601</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.3279</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32918</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32468</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.3182</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32623</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31706</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31702</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.32814</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32542</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31714</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.36915</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32376</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31952</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.32189</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.32159</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.3237</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.33198</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32993</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32269</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32255</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.32985</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.32972</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33228</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33713</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34499</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.35869</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.35498</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.35658</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35374</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35458</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.3663</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.34972</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.35937</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34576</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.35871</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.35875</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36079</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.34873</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.38243</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.37874</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.38071</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38432</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.42468</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.4112</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.37869</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.37695</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.65237</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.77319</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.45099</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.29903</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45741</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39422</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.34963</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35215</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35837</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33905</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34371</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.30687</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41029</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37593</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37055</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36177</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35895</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35865</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36181</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35724</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.35998</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35877</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35265</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.35979</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.35999</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35566</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35186</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35896</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.35925</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35958</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.33461</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.36994</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35854</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35626</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.35983</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.35983</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37756</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36562</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37935</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35628</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35624</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35088</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35157</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35702</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34872</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.3294</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.31942</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33442</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32726</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.33265</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.41317</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.34138</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.2855</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.28497</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.20133</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.26251</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.28125</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.33752</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.28031</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.22406</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.27944</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28602</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.28149</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.29041</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.29548</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30669</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.34931</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.32483</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.30359</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.89103</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.3623</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.33374</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.33852</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.34366</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.36432</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.79759</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.79162</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.56298</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.79544</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.78288</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.36805</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.32795</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.36497</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.43901</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.38816</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.42416</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.6476900000000001</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.6055199999999999</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.5846</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.46531</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.67201</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.46363</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.82511</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.43496</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>1.04795</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.40796</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.37499</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.36102</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.47649</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.42963</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.41769</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37798</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37455</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36688</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.35976</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34276</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.48952</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.53826</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.48518</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.49414</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41617</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.39684</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40225</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.40923</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.40727</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41547</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.39822</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39425</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.40957</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.40794</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39336</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38739</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.41783</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38721</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41567</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.38962</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.39888</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.39897</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41139</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.39871</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.44898</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.44716</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.5575</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.49875</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.44932</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.31944</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.45018</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.47462</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.37581</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.38635</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.41974</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.44917</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.5151399999999999</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.68523</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.4675</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.30484</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.34234</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.37919</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.40939</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.40612</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.41996</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.3369</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.35382</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.2893</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.34361</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.34302</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.36267</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.35537</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.38181</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.6549299999999999</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.37554</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.35238</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.24681</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.30374</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.38314</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.35567</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.34239</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33521</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.35583</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.33312</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.37491</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.35977</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.37499</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.35737</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.36356</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.35659</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.39075</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.34172</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.42112</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.44148</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.49369</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.43989</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.5105</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.51066</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.5450900000000001</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.69584</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.72878</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.39897</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.67162</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.8118</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.59238</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.52404</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.83121</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.77124</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.62813</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.67508</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.45015</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.48036</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.482</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.47652</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.46808</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41719</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.5565099999999999</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.42984</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.44128</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.45484</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.43362</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42421</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44484</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41533</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.39888</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.45362</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39719</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40433</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39556</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38608</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.3779</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37294</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.35983</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35663</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36561</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37365</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37046</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.35957</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35928</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36561</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38498</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.3894</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37874</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36544</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35463</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37868</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39856</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.37131</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.38627</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.40017</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39357</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38557</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35128</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36907</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.3444700000000001</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.34249</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.35847</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.38938</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.21065</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.39573</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.36354</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.35229</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.04772</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.3765</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.35175</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.40361</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.35335</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.45069</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.39009</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.46171</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.32954</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.31314</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.11868</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.18021</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.29771</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29416</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.31925</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35132</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.34887</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34794</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.35074</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.38783</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.38578</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.38318</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>1.1454</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.41673</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36941</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.43093</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.43842</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.4167</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.3867</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.3821</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38475</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.38998</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.40819</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40826</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.3452</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.3705</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37634</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.39575</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.35983</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.3782799999999999</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35483</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39881</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.37886</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37444</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.35835</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39423</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37937</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36472</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44417</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.36261</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.39838</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.39788</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.35869</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.37794</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.34903</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37581</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.35651</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35602</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35273</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.34895</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35646</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34519</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35105</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34799</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.33759</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33861</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.33918</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.33898</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.3439700000000001</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.32808</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.32896</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.32769</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.32755</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.33595</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.31764</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.30814</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.30388</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.31375</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.28221</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.31853</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.3141</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.30798</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.22624</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.2874</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.23087</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.29067</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.25066</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.26864</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.13921</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.29603</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.29924</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.32965</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.25414</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04301</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.25091</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.30467</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.17178</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.18372</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.28682</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.30969</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.33014</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.22931</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.24993</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.2685</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.23277</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27577</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28432</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.2837</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.32869</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.32756</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.30796</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.35224</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34739</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.35251</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.36096</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.35482</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.35858</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.37638</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.3619</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34444</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.31051</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.35715</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.35843</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.38373</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.35567</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.37156</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.37052</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.37277</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.3449</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.36547</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.38174</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.34044</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36282</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.36723</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.35889</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.34752</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.34705</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.34771</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.34719</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.3494</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.3209</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32597</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33716</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34073</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.34479</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.33806</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.32766</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.3225</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.31761</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.3175</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.30636</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.30805</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31304</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.30979</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.3071</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.30798</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.30797</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30399</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30399</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.30639</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.30479</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.3032</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30399</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.30443</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.30919</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.30822</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.28801</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.25153</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.23705</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.16307</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.20159</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.2498</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.0185</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.03079</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04884</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.11444</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.01893</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03882</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04887</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.008140000000000001</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.03364</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.02921</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04659000000000001</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04586</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02247</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.01883</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04892000000000001</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.18962</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04887</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.0489</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04865</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00126</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.31571</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04894</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04871</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.0489</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.03376</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04885</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04849000000000001</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.04291</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.18311</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.19236</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.23267</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.28063</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.26133</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.26298</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.25932</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.26649</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.28072</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.30161</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.2887</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.28742</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.27995</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.30725</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.29618</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.30621</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.28615</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.30461</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.28518</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.3008</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.29218</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.32257</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.41092</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.32437</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.33161</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.3077</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.28935</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.2868</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.2814700000000001</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.2797</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.3217</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.12383</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29804</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.56374</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.34718</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.14508</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.31092</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.28435</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.27509</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.25321</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.29551</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.30396</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.28868</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.26372</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.24016</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.22867</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.25745</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.24728</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.21171</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.23733</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.2399</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.27517</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.26204</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.26188</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.24235</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.29667</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.26792</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.30247</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.35282</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.29961</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.27198</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.2738</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.21827</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.14225</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.62817</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.60429</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.6445299999999999</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.57909</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.15711</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.11722</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.2354</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.17702</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.10627</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.11633</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.06744</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.2255</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.09888</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.30935</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.01454</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.02967</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.08899</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.16858</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.0276</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.1076</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.11819</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.13741</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.02251</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.08971</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.10347</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.10169</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.14145</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.26057</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29706</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.28162</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.3227</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.33506</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.33485</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.33044</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.34013</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.33468</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.34145</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.33262</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.36078</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.36416</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.37808</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.34166</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.39255</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.38145</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.46749</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.37703</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.37771</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.36517</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.36482</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.35589</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.37059</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.36039</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.3695</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.37654</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.33445</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.32852</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.32836</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.32921</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.32947</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.33804</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32301</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33011</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.35489</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.3708</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.38136</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.34317</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.34442</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.33009</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.33047</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.33012</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.33537</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.32821</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.34074</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.3382</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.33508</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32714</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34228</v>
+      </c>
+      <c r="R138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.32441</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.32083</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.30852</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.32619</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.31846</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.31945</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.31726</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.32267</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.33293</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.57451</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.55816</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.4227</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.4378</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.35289</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.33791</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.34551</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.39262</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.45549</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.37383</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.48005</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.39471</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.45076</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.38742</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.38105</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.37148</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.4512</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.33807</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.31507</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.33225</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.33732</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31296</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.14274</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.28049</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.27028</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.3057</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.33122</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.33631</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.32161</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.3364</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.28018</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.31955</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31234</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.29224</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.31321</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31903</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32275</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32788</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.33337</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.3262</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.3492</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.34693</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.34864</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.35017</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.34943</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.35727</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33572</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.36114</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.3623</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.33708</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.35226</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.34116</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.36776</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.37559</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.30484</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.5037</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.3562</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.4079</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.3597</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.38837</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.36016</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.36247</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.35577</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36935</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.34852</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.30933</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.32939</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.31985</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.32843</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.32832</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.36795</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.33035</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.33038</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.27873</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.31556</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.31957</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.3343</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32829</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.33033</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33233</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.33956</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34477</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.30503</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.34806</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.33983</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33474</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.31795</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.31847</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34595</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33068</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.33961</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35329</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32265</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.3677</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35449</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.36888</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35888</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.36119</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.38133</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.32955</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.35488</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.37504</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.62782</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.33772</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.59004</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.36668</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.51079</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.38219</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.36841</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.36324</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.3676</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.31258</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.35718</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.35014</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.44847</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.36369</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.3122799999999999</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.3533</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.3235</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.34484</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.2643</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.34341</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34884</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.35248</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32952</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.28713</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.29019</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.34261</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.34283</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.35216</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.34234</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.36862</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.37448</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.4188</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.40688</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.49625</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.50647</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.46929</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.48933</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.42752</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.62187</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.4228</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.44487</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.49816</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.35971</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.34624</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.38417</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.36921</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.37986</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.36339</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.38974</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.41568</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.38978</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.38455</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.37001</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45543</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.39996</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38264</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.40455</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.38308</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.15836</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.3724</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.3439</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.3676</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34695</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.48188</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40395</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40386</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39571</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38031</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.35969</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37481</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37395</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37814</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37652</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36849</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36659</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36111</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.35999</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35914</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.36012</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35514</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32727</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35586</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.34987</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.35034</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34684</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35013</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.35899</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37015</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.39764</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37474</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.37119</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.36258</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.36119</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.37341</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.36256</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.42065</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.42769</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.39524</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.38872</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.47324</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.41144</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.38414</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.30758</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.36013</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.33544</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.3736</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.27868</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.38709</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.36932</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.36809</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29461</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.31771</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.33675</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.34152</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.32386</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.32189</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.34175</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.35326</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.3489</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.36819</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.36464</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.31103</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.36424</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.36282</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.39798</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.38969</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.4075299999999999</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.37768</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.41424</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.56677</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.43339</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.5238700000000001</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.47319</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.43995</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.51562</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.5834600000000001</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.58685</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.38656</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.42416</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.527</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.5106700000000001</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.55328</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.47287</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.38464</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.5185</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.42721</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.70113</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.86883</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.58441</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.58382</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39703</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.44206</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.39848</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.37426</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.37708</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.36701</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37238</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.25723</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36935</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.32881</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.36594</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.33334</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33573</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.3453</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.32333</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33307</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.34171</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.33734</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.35351</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.33552</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33839</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.3371499999999999</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.31365</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.32221</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.31963</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.31812</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.3161</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.31888</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.31793</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.30898</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.30963</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.34885</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.36911</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.32352</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.31098</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.30538</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.30008</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.29622</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.33269</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.29701</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.31962</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.32008</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.22816</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.2776</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.32682</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.1819</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.31005</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.16237</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.07595</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.44681</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.38505</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.22969</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.04429</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.22094</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.17653</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.01187</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.33154</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.26709</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.17305</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.06609000000000001</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.06055</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.08073999999999999</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.17768</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.08796</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.06311</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.17989</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.16234</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.24052</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.29429</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.32551</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.32173</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.32562</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.38989</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.35766</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.36726</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.39149</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.36343</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.37177</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.25009</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.35199</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.36518</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.35732</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.31032</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.37768</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.38409</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.42936</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.382</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.40768</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.41606</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.38841</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.40164</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.4282</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.39294</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.38794</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.42544</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.37702</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.43481</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.38298</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.37495</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.35659</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.33972</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.35943</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.86538</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.37164</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.47044</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.42469</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.39515</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.33644</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.37998</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.38579</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.37414</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.34878</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.35533</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.3430299999999999</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.3654</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.34947</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.35073</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.37201</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.38476</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.35707</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.35013</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.35908</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.35392</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.35637</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.35595</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.35703</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.34163</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.38592</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.33765</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.35026</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.33516</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.30389</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.30952</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.33473</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.32942</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.31844</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.3024</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.26299</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.2566000000000001</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.2782</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.24916</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.11436</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.2476</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.26599</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.38151</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.41139</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.7461100000000001</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.42619</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.00391</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.01939</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.04867</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.02034</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.02581</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.24983</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.3429700000000001</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.34859</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.04849000000000001</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.23823</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.35231</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>1.10696</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>1.09611</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.28632</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.32632</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.32428</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.32703</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.33557</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.32091</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.34746</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.33446</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.49879</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.43139</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.42208</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.36216</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.37296</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.39087</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.3648</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.3422</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.39829</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.5809299999999999</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.36213</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.37024</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.36468</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.36733</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.37201</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.36038</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.37979</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.34128</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.41235</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.39672</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.37059</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.38575</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.35768</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.35756</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.35059</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.36283</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.35923</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.33404</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.61572</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.36914</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.37055</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.32344</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.35506</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.3491</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.35212</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.34143</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.45531</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.34056</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.39093</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.37165</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.34476</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.34298</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.34761</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.32446</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.33336</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.33807</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.32584</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.32955</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.3285</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.34379</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.33429</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.34329</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.33735</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.33206</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.3455299999999999</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.33316</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.30978</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.28018</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.2578</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.23015</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.14391</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.20571</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.22931</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.23108</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.11417</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.15015</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.00207</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04727000000000001</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.04737</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.04659000000000001</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.04735</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.04693</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.04179</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.07848999999999999</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.03007</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.06302000000000001</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.09670999999999999</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.17014</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.19567</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.12037</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.25444</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.22929</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.12394</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.05536</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.26225</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.14617</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.11727</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.23647</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.18481</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.23611</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.24303</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.20311</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.24376</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.27367</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.27541</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.29964</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.30437</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.30696</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.31163</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.33235</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.33893</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.35888</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.33665</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.32981</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.32502</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.35065</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.37773</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.35146</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.36264</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.36239</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.36092</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.39019</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.3959</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.46723</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.38579</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.38337</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.37898</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.38894</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.3668</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.37669</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.38158</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.36589</v>
       </c>
     </row>
   </sheetData>
